--- a/output/MIXI.xlsx
+++ b/output/MIXI.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BLUE STORM</t>
+          <t>ALLURE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inspired by Bleu de Chanel</t>
+          <t>Inspired by Chanel Allure Homme Sport</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -466,16 +466,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>ALMOND SMOKE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inspired by Imagination – Louis Vuitton</t>
+          <t>Inspired by Guerlain L’Homme Idéal Extrême</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4">
@@ -486,16 +486,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Masterpiece</t>
+          <t>AMBER DUSK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inspired by Stronger With You Intensely</t>
+          <t>Inspired by Maison Francis Kurkdjian Grand Soir</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5">
@@ -506,12 +506,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WILD NOIR</t>
+          <t>ARABIAN BOOZY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inspired by Sauvage dior</t>
+          <t>Inspired by Khamrah</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -526,16 +526,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VENTOR</t>
+          <t>ARABIAN MAGIC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inspired by Layton – Parfums de Marly</t>
+          <t>Inspired by Arabian Oud Kalemat</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7">
@@ -546,16 +546,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DARK BLUE</t>
+          <t>ATLANTIC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inspired by Y - Yves Saint Laurent</t>
+          <t>Inspired by Pacific Chill</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -566,16 +566,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIXI 11</t>
+          <t>BLACK AURA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inspired by Bianco Latte</t>
+          <t>Inspired by Black Afgano</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9">
@@ -586,12 +586,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LYNX</t>
+          <t>BLACK LEGACY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inspired by Le Male Elixir</t>
+          <t>Inspired by Paco Rabanne Black XS L’Exces</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -606,16 +606,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IVENTO</t>
+          <t>BLUE ELITE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inspired by Creed Aventus</t>
+          <t>Inspired by Chanel Bleu de Chanel L’Exclusif</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>550</v>
+        <v>950</v>
       </c>
     </row>
     <row r="11">
@@ -626,16 +626,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SWEET STORM</t>
+          <t>BLUE KING</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inspired by Ultra Male</t>
+          <t>Inspired by Blue Talisman</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="12">
@@ -646,12 +646,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARABIAN BOOZY</t>
+          <t>BLUE STORM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inspired by Khamrah</t>
+          <t>Inspired by Bleu de Chanel</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -666,16 +666,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IMPERIAL PINE</t>
+          <t>BLUE WAVE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inspired by Hacivat – Nishane</t>
+          <t>Inspired by Dylan Blue</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14">
@@ -686,16 +686,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HAWAI</t>
+          <t>BOOZY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inspired by Erba Pura – Xerjoff</t>
+          <t>Inspired by Angels’ Share</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15">
@@ -706,16 +706,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IMPERIAL TOBACCO</t>
+          <t>BOOZY INTENSE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inspired by Tobacco Vanille – Tom Ford</t>
+          <t>Inspired by Angels’ Share Paradis</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
     </row>
     <row r="16">
@@ -726,16 +726,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRAND ICON</t>
+          <t>BORKAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inspired by The One from Dolce &amp; Gabbana</t>
+          <t>Inspired by Imperial Valley</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="17">
@@ -746,12 +746,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATLANTIC</t>
+          <t>CASAMORATI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inspired by Pacific Chill</t>
+          <t>Inspired by Accento</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -766,16 +766,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIXI 33</t>
+          <t>CRISTAL ROUGE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inspired by Khamrah Qahwa</t>
+          <t>Inspired by Hibiscus Mahajád</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19">
@@ -786,16 +786,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAJESTIC</t>
+          <t>CRISTAL SAFFRON</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inspired by stronger with you</t>
+          <t>Inspired by Baccarat Rouge</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20">
@@ -806,12 +806,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TITARO</t>
+          <t>CROCODILE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inspired by Eros</t>
+          <t>Inspired by lacoste white</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -826,16 +826,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SERENO</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inspired by Acqua di Giò</t>
+          <t>Inspired by Guidance</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="22">
@@ -846,16 +846,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BLACK AURA</t>
+          <t>CRYSTAL MOUNTAIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inspired by Black Afgano</t>
+          <t>Inspired by Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23">
@@ -866,16 +866,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FOREST GARDEN</t>
+          <t>DARK BLUE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inspired by Le Beau Paradise Garden</t>
+          <t>Inspired by Y - Yves Saint Laurent</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24">
@@ -886,16 +886,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ALLURE</t>
+          <t>DARK IRIS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inspired by Chanel Allure Homme Sport</t>
+          <t>Inspired by Dior Homme Intense</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25">
@@ -906,16 +906,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DARK IRIS</t>
+          <t>DARK LEATHER</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inspired by Dior Homme Intense</t>
+          <t>Inspired by Tom Ford Ombre Leather</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26">
@@ -926,12 +926,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>DARK VOLT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inspired by Uomo Born in Roma Intense</t>
+          <t>Inspired by Spicebomb Extreme</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -946,16 +946,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>‏SUN HIT</t>
+          <t>DEEP TOUCH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inspired by Summer Hammer</t>
+          <t>Inspired by La Nuit de L’Homme</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28">
@@ -966,16 +966,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOLDEN DESERT</t>
+          <t>FOREST GARDEN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inspired by madawi</t>
+          <t>Inspired by Le Beau Paradise Garden</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29">
@@ -986,12 +986,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIXI 7</t>
+          <t>FRENCH OUD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inspired by Hugo Boss The Scent</t>
+          <t>Inspired by Oud Bouquet</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1006,16 +1006,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CASAMORATI</t>
+          <t>GOLDEN DESERT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inspired by Accento</t>
+          <t>Inspired by madawi</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>‏MAJESTIC ABSOLUTELY</t>
+          <t>GRAND ICON</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inspired by Giorgio Armani Stronger With You Absolutely</t>
+          <t>Inspired by The One from Dolce &amp; Gabbana</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1046,16 +1046,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>GRAND MAFIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inspired by Symphony – Louis Vuitton</t>
+          <t>Inspired by Side Effect</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>950</v>
+        <v>850</v>
       </c>
     </row>
     <row r="33">
@@ -1066,16 +1066,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BOOZY INTENSE</t>
+          <t>HAWAI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inspired by Angels’ Share Paradis</t>
+          <t>Inspired by Erba Pura – Xerjoff</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>850</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34">
@@ -1086,16 +1086,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DARK VOLT</t>
+          <t>HAWAI INTENSE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inspired by Spicebomb Extreme</t>
+          <t>Inspired by Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="35">
@@ -1106,16 +1106,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BLUE WAVE</t>
+          <t>HONEY SMOKE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inspired by Dylan Blue</t>
+          <t>Inspired by Naxos</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36">
@@ -1126,16 +1126,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CROCODILE</t>
+          <t>IMPERIAL PINE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inspired by lacoste white</t>
+          <t>Inspired by Hacivat – Nishane</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="37">
@@ -1146,16 +1146,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WILD NOIR ELIXIR</t>
+          <t>IMPERIAL TOBACCO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inspired by Dior Sauvage Elixir</t>
+          <t>Inspired by Tobacco Vanille – Tom Ford</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="38">
@@ -1166,16 +1166,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TROPIC FIRE</t>
+          <t>IMPERIAL WOOD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inspired by *od of Fire</t>
+          <t>Inspired by Essential Parfums Bois Impérial</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
     </row>
     <row r="39">
@@ -1186,16 +1186,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RAVADOR</t>
+          <t>INVECTO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inspired by Althaïr</t>
+          <t>Inspired by paco rabanne Invictus</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="40">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CRISTAL SAFFRON</t>
+          <t>IVENTO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inspired by Baccarat Rouge</t>
+          <t>Inspired by Creed Aventus</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="41">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ORCHID NOIR</t>
+          <t>LUXOR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Black Orchid</t>
+          <t>Inspired by Gentleman Reserve Privée</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DEEP TOUCH</t>
+          <t>LYNX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inspired by La Nuit de L’Homme</t>
+          <t>Inspired by Le Male Elixir</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CRYSTAL MOUNTAIN</t>
+          <t>LYNX ABSOLU</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inspired by Creed Silver Mountain Water</t>
+          <t>Inspired by Jean Paul Gaultier Le Male Elixir Absolu</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1286,16 +1286,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INVECTO</t>
+          <t>MAESTRO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inspired by paco rabanne Invictus</t>
+          <t>Inspired by Symphony – Louis Vuitton</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>550</v>
+        <v>950</v>
       </c>
     </row>
     <row r="45">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FRENCH OUD</t>
+          <t>MAJESTIC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inspired by Oud Bouquet</t>
+          <t>Inspired by stronger with you</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BLUE ELITE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Inspired by Chanel Bleu de Chanel L’Exclusif</t>
+          <t>Inspired by Imagination – Louis Vuitton</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row r="47">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRISTAL ROUGE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inspired by Hibiscus Mahajád</t>
+          <t>Inspired by Uomo Born in Roma Intense</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WANTED ICON</t>
+          <t>MILLIONAIRE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inspired by The Most Wanted</t>
+          <t>Inspired by Paco Rabanne One Million</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1386,16 +1386,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TIGER</t>
+          <t>MIXI 11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inspired by Tygar – Bvlgari</t>
+          <t>Inspired by Bianco Latte</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DARK LEATHER</t>
+          <t>MIXI 33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Ombre Leather</t>
+          <t>Inspired by Khamrah Qahwa</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OUD NOMAD</t>
+          <t>MIXI 50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inspired by Louis Vuitton Ombre Nomade</t>
+          <t>Inspired by Amouage Purpose 50</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
     </row>
     <row r="52">
@@ -1446,16 +1446,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RED SEA</t>
+          <t>MIXI 7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inspired by Xerjoff 40 Knots</t>
+          <t>Inspired by Hugo Boss The Scent</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53">
@@ -1466,16 +1466,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ARABIAN MAGIC</t>
+          <t>MORE THAN OUD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Inspired by Arabian Oud Kalemat</t>
+          <t>Inspired by عود الف ليله وليله</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="54">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>MORE THAN VANILLA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Inspired by Guidance</t>
+          <t>Inspired by bare vanilla</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="55">
@@ -1506,16 +1506,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MIXI 50</t>
+          <t>Masterpiece</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Purpose 50</t>
+          <t>Inspired by Stronger With You Intensely</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56">
@@ -1526,16 +1526,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>‏SILK OUD</t>
+          <t>NOBLE ABSOLU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Oud Wood</t>
+          <t>Inspired by Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="57">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>‏MAGMA</t>
+          <t>ORCHID NOIR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inspired by Orto Parisi Megamare</t>
+          <t>Inspired by Tom Ford Black Orchid</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58">
@@ -1566,16 +1566,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IMPERIAL WOOD</t>
+          <t>OUD NOMAD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Inspired by Essential Parfums Bois Impérial</t>
+          <t>Inspired by Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row r="59">
@@ -1586,16 +1586,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BORKAN</t>
+          <t>QARAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Inspired by Imperial Valley</t>
+          <t>Inspired by Amouage Decision</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>850</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="60">
@@ -1606,16 +1606,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MILLIONAIRE</t>
+          <t>RAVADOR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Inspired by Paco Rabanne One Million</t>
+          <t>Inspired by Althaïr</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LUXOR</t>
+          <t>RED SEA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inspired by Gentleman Reserve Privée</t>
+          <t>Inspired by Xerjoff 40 Knots</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>‏Noble</t>
+          <t>SERENO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inspired by Hugo Boss Boss Bottled</t>
+          <t>Inspired by Acqua di Giò</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BLACK LEGACY</t>
+          <t>SILVER VEIL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inspired by Paco Rabanne Black XS L’Exces</t>
+          <t>Inspired by Silver Scent</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1686,16 +1686,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WINTER PALACE</t>
+          <t>SWEET STORM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inspired by Alexandria II – Xerjoff</t>
+          <t>Inspired by Ultra Male</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65">
@@ -1706,16 +1706,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MORE THAN VANILLA</t>
+          <t>TIGER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inspired by bare vanilla</t>
+          <t>Inspired by Tygar – Bvlgari</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="66">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LYNX ABSOLU</t>
+          <t>TITARO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inspired by Jean Paul Gaultier Le Male Elixir Absolu</t>
+          <t>Inspired by Eros</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -1746,16 +1746,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>‏TIMELESS</t>
+          <t>TORENDO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inspired by Louis Vuitton Stellar Times</t>
+          <t>Inspired by Rosendo Mateu Nº 5</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>950</v>
+        <v>650</v>
       </c>
     </row>
     <row r="68">
@@ -1786,16 +1786,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>‏ICONIC</t>
+          <t>TROPIC FIRE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inspired by Montblanc Legend</t>
+          <t>Inspired by *od of Fire</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="70">
@@ -1806,16 +1806,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HAWAI INTENSE</t>
+          <t>VANILUXE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inspired by Tiziana Terenzi Kirke</t>
+          <t>Inspired by Ani – Nishane</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>850</v>
+        <v>650</v>
       </c>
     </row>
     <row r="71">
@@ -1826,16 +1826,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NOBLE ABSOLU</t>
+          <t>VELVET CHERRY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inspired by Boss Bottled Absolu</t>
+          <t>Inspired by Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="72">
@@ -1846,16 +1846,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BOOZY</t>
+          <t>VENTOR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Inspired by Angels’ Share</t>
+          <t>Inspired by Layton – Parfums de Marly</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="73">
@@ -1866,16 +1866,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TORENDO</t>
+          <t>WANTED ICON</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inspired by Rosendo Mateu Nº 5</t>
+          <t>Inspired by The Most Wanted</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="74">
@@ -1886,16 +1886,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>‏GREATNESS</t>
+          <t>WILD NOIR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Inspired by Initio Oud for Greatness</t>
+          <t>Inspired by Sauvage dior</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="75">
@@ -1906,16 +1906,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GRAND MAFIA</t>
+          <t>WILD NOIR ELIXIR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Inspired by Side Effect</t>
+          <t>Inspired by Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HONEY SMOKE</t>
+          <t>WINTER PALACE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inspired by Naxos</t>
+          <t>Inspired by Alexandria II – Xerjoff</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
     </row>
     <row r="77">
@@ -1946,16 +1946,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SILVER VEIL</t>
+          <t>‏GREATNESS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inspired by Silver Scent</t>
+          <t>Inspired by Initio Oud for Greatness</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="78">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ALMOND SMOKE</t>
+          <t>‏HEATED</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Inspired by Guerlain L’Homme Idéal Extrême</t>
+          <t>Inspired by By Kilian Smoking Hot</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1986,16 +1986,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VELVET CHERRY</t>
+          <t>‏ICONIC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Lost Cherry</t>
+          <t>Inspired by Montblanc Legend</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="80">
@@ -2006,16 +2006,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VANILUXE</t>
+          <t>‏MAGMA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Inspired by Ani – Nishane</t>
+          <t>Inspired by Orto Parisi Megamare</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="81">
@@ -2026,16 +2026,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>‏SMOLDER</t>
+          <t>‏MAJESTIC ABSOLUTELY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Interlude Man</t>
+          <t>Inspired by Giorgio Armani Stronger With You Absolutely</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="82">
@@ -2046,16 +2046,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AMBER DUSK</t>
+          <t>‏Noble</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Inspired by Maison Francis Kurkdjian Grand Soir</t>
+          <t>Inspired by Hugo Boss Boss Bottled</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="83">
@@ -2066,16 +2066,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>‏UMBRA</t>
+          <t>‏SILK OUD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Inspired by Blonde Amber</t>
+          <t>Inspired by Tom Ford Oud Wood</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="84">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MORE THAN OUD</t>
+          <t>‏SMOLDER</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Inspired by عود الف ليله وليله</t>
+          <t>Inspired by Amouage Interlude Man</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2106,16 +2106,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>‏HEATED</t>
+          <t>‏SUN HIT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Inspired by By Kilian Smoking Hot</t>
+          <t>Inspired by Summer Hammer</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
     </row>
     <row r="86">
@@ -2126,16 +2126,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BLUE KING</t>
+          <t>‏TIMELESS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Inspired by Blue Talisman</t>
+          <t>Inspired by Louis Vuitton Stellar Times</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
     </row>
     <row r="87">
@@ -2146,72 +2146,72 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>QARAR</t>
+          <t>‏UMBRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Decision</t>
+          <t>Inspired by Blonde Amber</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1050</v>
+        <v>950</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MIXI 11</t>
+          <t>ALMOND SMOKE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Inspired by Bianco Latte</t>
+          <t>Inspired by Guerlain L’Homme Idéal Extrême</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ARABIAN BOOZY</t>
+          <t>AMBER DUSK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Inspired by Khamrah</t>
+          <t>Inspired by Maison Francis Kurkdjian Grand Soir</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BERRY BLOOM</t>
+          <t>ARABIAN BOOZY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Inspired by Burberry Her</t>
+          <t>Inspired by Khamrah</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2221,17 +2221,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MIXI 33</t>
+          <t>ARABIAN MAGIC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Inspired by Khamrah Qahwa</t>
+          <t>Inspired by Arabian Oud Kalemat</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2241,97 +2241,97 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PRINCESS</t>
+          <t>ATLANTIC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Inspired by Donna Born in Roma Intense – Valentino</t>
+          <t>Inspired by Pacific Chill</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>‏SUN HIT</t>
+          <t>BLACK AURA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inspired by Summer Hammer</t>
+          <t>Inspired by Black Afgano</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GOLDEN DESERT</t>
+          <t>BOOZY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Inspired by madawi</t>
+          <t>Inspired by Angels’ Share</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SILKEN ROSE</t>
+          <t>BOOZY INTENSE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Inspired by Prada Paradoxe</t>
+          <t>Inspired by Angels’ Share Paradis</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BOOZY INTENSE</t>
+          <t>BORKAN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inspired by Angels’ Share Paradis</t>
+          <t>Inspired by Imperial Valley</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2341,17 +2341,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CRISTAL SAFFRON</t>
+          <t>CASAMORATI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Inspired by Baccarat Rouge</t>
+          <t>Inspired by Accento</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2361,97 +2361,97 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ORCHID NOIR</t>
+          <t>CRISTAL ROUGE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Black Orchid</t>
+          <t>Inspired by Hibiscus Mahajád</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>‏ELORA</t>
+          <t>CRISTAL SAFFRON</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Inspired by Lancôme Idôle</t>
+          <t>Inspired by Baccarat Rouge</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRENCH OUD</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Inspired by Oud Bouquet</t>
+          <t>Inspired by Guidance</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CRISTAL ROUGE</t>
+          <t>DARK LEATHER</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Inspired by Hibiscus Mahajád</t>
+          <t>Inspired by Tom Ford Ombre Leather</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BALLERINA</t>
+          <t>FRENCH OUD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Inspired by La Belle Le Parfum</t>
+          <t>Inspired by Oud Bouquet</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2461,17 +2461,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LIBRA</t>
+          <t>GOLDEN DESERT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Inspired by Libre</t>
+          <t>Inspired by madawi</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2481,57 +2481,57 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ARABIAN MAGIC</t>
+          <t>HAWAI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Inspired by Arabian Oud Kalemat</t>
+          <t>Inspired by Erba Pura – Xerjoff</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HEAVEN</t>
+          <t>HAWAI INTENSE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Inspired by Love Is Heavenly</t>
+          <t>Inspired by Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>HONEY SMOKE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Inspired by Guidance</t>
+          <t>Inspired by Naxos</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2541,97 +2541,97 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SILKEN MARSHMALLOW</t>
+          <t>IMPERIAL TOBACCO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Inspired by Yum Boujee Marshmallow – Kayali</t>
+          <t>Inspired by Tobacco Vanille – Tom Ford</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ROUGE POMME</t>
+          <t>IMPERIAL WOOD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Inspired by Eden Juicy Apple</t>
+          <t>Inspired by Essential Parfums Bois Impérial</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MIXI 50</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Purpose 50</t>
+          <t>Inspired by Imagination – Louis Vuitton</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>850</v>
+        <v>750</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LYCHEE</t>
+          <t>MIXI 11</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Inspired by Delina de Marly</t>
+          <t>Inspired by Bianco Latte</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>‏VELA ROUGE</t>
+          <t>MIXI 33</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Inspired by Giorgio Armani Sì Passione</t>
+          <t>Inspired by Khamrah Qahwa</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -2641,57 +2641,57 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RED HONEY</t>
+          <t>MIXI 50</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inspired by Scandal</t>
+          <t>Inspired by Amouage Purpose 50</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MADEMOISELLE</t>
+          <t>MORE THAN OUD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Inspired by Chanel Coco Mademoiselle</t>
+          <t>Inspired by عود الف ليله وليله</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ROSELLA</t>
+          <t>MORE THAN VANILLA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Inspired by Mancera Rose Vanille</t>
+          <t>Inspired by bare vanilla</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -2701,17 +2701,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MORE THAN VANILLA</t>
+          <t>ORCHID NOIR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Inspired by bare vanilla</t>
+          <t>Inspired by Tom Ford Black Orchid</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -2721,177 +2721,177 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>‏TIMELESS</t>
+          <t>OUD NOMAD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Inspired by Louis Vuitton Stellar Times</t>
+          <t>Inspired by Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ELYSIA</t>
+          <t>QARAR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Inspired by Billie Eilish</t>
+          <t>Inspired by Amouage Decision</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>550</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HAWAI INTENSE</t>
+          <t>TORENDO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Inspired by Tiziana Terenzi Kirke</t>
+          <t>Inspired by Rosendo Mateu Nº 5</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>850</v>
+        <v>650</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GOLDEN GIRL</t>
+          <t>TROPIC FIRE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Inspired by Carolina Herrera Good Girl</t>
+          <t>Inspired by *od of Fire</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BOOZY</t>
+          <t>VANILUXE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Inspired by Angels’ Share</t>
+          <t>Inspired by Ani – Nishane</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DARK ADDICTION</t>
+          <t>VELVET CHERRY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Inspired by Yves Saint Laurent Black Opium</t>
+          <t>Inspired by Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>‏GREATNESS</t>
+          <t>VENTOR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Inspired by Initio Oud for Greatness</t>
+          <t>Inspired by Layton – Parfums de Marly</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GOLDEN QUEEN</t>
+          <t>WINTER PALACE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Inspired by Burberry Gold</t>
+          <t>Inspired by Alexandria II – Xerjoff</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>550</v>
+        <v>950</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VELVET CHERRY</t>
+          <t>‏GREATNESS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Lost Cherry</t>
+          <t>Inspired by Initio Oud for Greatness</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -2901,57 +2901,57 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>‏VELORA</t>
+          <t>‏HEATED</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Inspired by Lancôme La Vie Est Belle</t>
+          <t>Inspired by By Kilian Smoking Hot</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>‏Rose d’Afrique</t>
+          <t>‏MAGMA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Inspired by Roberto Cavalli Roberto Cavalli</t>
+          <t>Inspired by Orto Parisi Megamare</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>‏DOMINA</t>
+          <t>‏SILK OUD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Inspired by Paco Rabanne Olympéa</t>
+          <t>Inspired by Tom Ford Oud Wood</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -2961,137 +2961,137 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>‏ELINA</t>
+          <t>‏SMOLDER</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inspired by Mugler Alien</t>
+          <t>Inspired by Amouage Interlude Man</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MORE THAN OUD</t>
+          <t>‏SUN HIT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Inspired by عود الف ليله وليله</t>
+          <t>Inspired by Summer Hammer</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>‏HEATED</t>
+          <t>‏TIMELESS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Inspired by By Kilian Smoking Hot</t>
+          <t>Inspired by Louis Vuitton Stellar Times</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>QARAR</t>
+          <t>‏UMBRA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Decision</t>
+          <t>Inspired by Blonde Amber</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1050</v>
+        <v>950</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>ARABIAN BOOZY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Inspired by Imagination – Louis Vuitton</t>
+          <t>Inspired by Khamrah</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VENTOR</t>
+          <t>ARABIAN MAGIC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Inspired by Layton – Parfums de Marly</t>
+          <t>Inspired by Arabian Oud Kalemat</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MIXI 11</t>
+          <t>BALLERINA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Inspired by Bianco Latte</t>
+          <t>Inspired by La Belle Le Parfum</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3101,17 +3101,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ARABIAN BOOZY</t>
+          <t>BERRY BLOOM</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Inspired by Khamrah</t>
+          <t>Inspired by Burberry Her</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -3121,137 +3121,137 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HAWAI</t>
+          <t>BOOZY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Inspired by Erba Pura – Xerjoff</t>
+          <t>Inspired by Angels’ Share</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IMPERIAL TOBACCO</t>
+          <t>BOOZY INTENSE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Inspired by Tobacco Vanille – Tom Ford</t>
+          <t>Inspired by Angels’ Share Paradis</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ATLANTIC</t>
+          <t>CRISTAL ROUGE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Inspired by Pacific Chill</t>
+          <t>Inspired by Hibiscus Mahajád</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MIXI 33</t>
+          <t>CRISTAL SAFFRON</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Inspired by Khamrah Qahwa</t>
+          <t>Inspired by Baccarat Rouge</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BLACK AURA</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Inspired by Black Afgano</t>
+          <t>Inspired by Guidance</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>‏SUN HIT</t>
+          <t>DARK ADDICTION</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Inspired by Summer Hammer</t>
+          <t>Inspired by Yves Saint Laurent Black Opium</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GOLDEN DESERT</t>
+          <t>ELYSIA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Inspired by madawi</t>
+          <t>Inspired by Billie Eilish</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3261,117 +3261,117 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CASAMORATI</t>
+          <t>FRENCH OUD</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Inspired by Accento</t>
+          <t>Inspired by Oud Bouquet</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BOOZY INTENSE</t>
+          <t>GOLDEN DESERT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Inspired by Angels’ Share Paradis</t>
+          <t>Inspired by madawi</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TROPIC FIRE</t>
+          <t>GOLDEN GIRL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Inspired by *od of Fire</t>
+          <t>Inspired by Carolina Herrera Good Girl</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CRISTAL SAFFRON</t>
+          <t>GOLDEN QUEEN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Inspired by Baccarat Rouge</t>
+          <t>Inspired by Burberry Gold</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ORCHID NOIR</t>
+          <t>HAWAI INTENSE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Black Orchid</t>
+          <t>Inspired by Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FRENCH OUD</t>
+          <t>HEAVEN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Inspired by Oud Bouquet</t>
+          <t>Inspired by Love Is Heavenly</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3381,77 +3381,77 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CRISTAL ROUGE</t>
+          <t>LIBRA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Inspired by Hibiscus Mahajád</t>
+          <t>Inspired by Libre</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DARK LEATHER</t>
+          <t>LYCHEE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Ombre Leather</t>
+          <t>Inspired by Delina de Marly</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OUD NOMAD</t>
+          <t>MADEMOISELLE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Inspired by Louis Vuitton Ombre Nomade</t>
+          <t>Inspired by Chanel Coco Mademoiselle</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ARABIAN MAGIC</t>
+          <t>MIXI 11</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Inspired by Arabian Oud Kalemat</t>
+          <t>Inspired by Bianco Latte</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3461,27 +3461,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>MIXI 33</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Inspired by Guidance</t>
+          <t>Inspired by Khamrah Qahwa</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3501,117 +3501,117 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>‏SILK OUD</t>
+          <t>MORE THAN OUD</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Oud Wood</t>
+          <t>Inspired by عود الف ليله وليله</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>‏MAGMA</t>
+          <t>MORE THAN VANILLA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Inspired by Orto Parisi Megamare</t>
+          <t>Inspired by bare vanilla</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IMPERIAL WOOD</t>
+          <t>ORCHID NOIR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Inspired by Essential Parfums Bois Impérial</t>
+          <t>Inspired by Tom Ford Black Orchid</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BORKAN</t>
+          <t>PRINCESS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Inspired by Imperial Valley</t>
+          <t>Inspired by Donna Born in Roma Intense – Valentino</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>WINTER PALACE</t>
+          <t>QARAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Inspired by Alexandria II – Xerjoff</t>
+          <t>Inspired by Amouage Decision</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>950</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MORE THAN VANILLA</t>
+          <t>RED HONEY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Inspired by bare vanilla</t>
+          <t>Inspired by Scandal</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -3621,97 +3621,97 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>‏TIMELESS</t>
+          <t>ROSELLA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Inspired by Louis Vuitton Stellar Times</t>
+          <t>Inspired by Mancera Rose Vanille</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HAWAI INTENSE</t>
+          <t>ROUGE POMME</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inspired by Tiziana Terenzi Kirke</t>
+          <t>Inspired by Eden Juicy Apple</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>850</v>
+        <v>650</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BOOZY</t>
+          <t>SILKEN MARSHMALLOW</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Inspired by Angels’ Share</t>
+          <t>Inspired by Yum Boujee Marshmallow – Kayali</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TORENDO</t>
+          <t>SILKEN ROSE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Inspired by Rosendo Mateu Nº 5</t>
+          <t>Inspired by Prada Paradoxe</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>‏GREATNESS</t>
+          <t>VELVET CHERRY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Inspired by Initio Oud for Greatness</t>
+          <t>Inspired by Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -3721,137 +3721,137 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HONEY SMOKE</t>
+          <t>‏DOMINA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inspired by Naxos</t>
+          <t>Inspired by Paco Rabanne Olympéa</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ALMOND SMOKE</t>
+          <t>‏ELINA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inspired by Guerlain L’Homme Idéal Extrême</t>
+          <t>Inspired by Mugler Alien</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>VELVET CHERRY</t>
+          <t>‏ELORA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Inspired by Tom Ford Lost Cherry</t>
+          <t>Inspired by Lancôme Idôle</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>VANILUXE</t>
+          <t>‏GREATNESS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Inspired by Ani – Nishane</t>
+          <t>Inspired by Initio Oud for Greatness</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>‏SMOLDER</t>
+          <t>‏HEATED</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Interlude Man</t>
+          <t>Inspired by By Kilian Smoking Hot</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>AMBER DUSK</t>
+          <t>‏Rose d’Afrique</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Inspired by Maison Francis Kurkdjian Grand Soir</t>
+          <t>Inspired by Roberto Cavalli Roberto Cavalli</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>‏UMBRA</t>
+          <t>‏SUN HIT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Inspired by Blonde Amber</t>
+          <t>Inspired by Summer Hammer</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -3861,61 +3861,61 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MORE THAN OUD</t>
+          <t>‏TIMELESS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Inspired by عود الف ليله وليله</t>
+          <t>Inspired by Louis Vuitton Stellar Times</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>‏HEATED</t>
+          <t>‏VELA ROUGE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inspired by By Kilian Smoking Hot</t>
+          <t>Inspired by Giorgio Armani Sì Passione</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>QARAR</t>
+          <t>‏VELORA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Inspired by Amouage Decision</t>
+          <t>Inspired by Lancôme La Vie Est Belle</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
